--- a/KatalonData/Bootstrap/VT-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-Data-Prod.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3226" uniqueCount="571">
   <si>
     <t>AppIDDemo</t>
   </si>
@@ -1509,6 +1509,243 @@
   </si>
   <si>
     <t>Tue Jul 07 16:41:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:23:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:26:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:31:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:38:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:43:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:47:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:49:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:12:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:13:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:14:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:16:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:08:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:10:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:12:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:14:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:17:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:43:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:48:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:49:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 04:41:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 05:00:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 05:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 05:44:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 06:06:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 06:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 06:52:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 07:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 07:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 07:52:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 08:13:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 08:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 20:54:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 21:17:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:59:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:04:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:06:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:13:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:37:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:40:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:41:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:43:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:45:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:28:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:29:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:31:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:33:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:34:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:36:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:37:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:38:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:39:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:42:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:45:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:48:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:52:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:53:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:54:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:57:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 08:59:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 09:00:55 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +2207,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
@@ -2071,7 +2308,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>457</v>
+        <v>560</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
@@ -2172,7 +2409,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>458</v>
+        <v>561</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
@@ -2273,7 +2510,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>459</v>
+        <v>562</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
@@ -2502,7 +2739,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>353</v>
+        <v>563</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
@@ -2606,7 +2843,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>354</v>
+        <v>564</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
@@ -2710,7 +2947,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>355</v>
+        <v>565</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
@@ -2814,7 +3051,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>356</v>
+        <v>566</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
@@ -3044,7 +3281,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>464</v>
+        <v>567</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
@@ -3145,7 +3382,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>465</v>
+        <v>568</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
@@ -3246,7 +3483,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>466</v>
+        <v>569</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
@@ -3347,7 +3584,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>467</v>
+        <v>570</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
@@ -3572,7 +3809,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>447</v>
+        <v>551</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
@@ -3673,7 +3910,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>448</v>
+        <v>552</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
@@ -3774,7 +4011,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>449</v>
+        <v>553</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
@@ -3875,7 +4112,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>450</v>
+        <v>554</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
@@ -4622,7 +4859,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>452</v>
+        <v>555</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>81</v>
@@ -4726,7 +4963,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>453</v>
+        <v>556</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>81</v>
@@ -4830,7 +5067,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>454</v>
+        <v>557</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>81</v>
@@ -4934,7 +5171,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>455</v>
+        <v>558</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>81</v>
@@ -5166,13 +5403,13 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>484</v>
+        <v>539</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -5273,13 +5510,13 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>485</v>
+        <v>540</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -5380,13 +5617,13 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>325</v>
+        <v>541</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>81</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
@@ -5487,13 +5724,13 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>326</v>
+        <v>542</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>81</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>477</v>
+        <v>521</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
@@ -5594,13 +5831,13 @@
         <v>78</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>327</v>
+        <v>543</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
@@ -5701,13 +5938,13 @@
         <v>78</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>328</v>
+        <v>544</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
@@ -5935,13 +6172,13 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>486</v>
+        <v>533</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>435</v>
+        <v>524</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -6042,13 +6279,13 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>487</v>
+        <v>534</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>436</v>
+        <v>525</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -6149,13 +6386,13 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>437</v>
+        <v>526</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -6256,13 +6493,13 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>489</v>
+        <v>536</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>438</v>
+        <v>527</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -6363,13 +6600,13 @@
         <v>78</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>490</v>
+        <v>537</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>439</v>
+        <v>528</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
@@ -6470,13 +6707,13 @@
         <v>78</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>491</v>
+        <v>538</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>78</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>440</v>
+        <v>529</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
@@ -6703,7 +6940,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>441</v>
+        <v>545</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>78</v>
@@ -6807,7 +7044,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>442</v>
+        <v>546</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>78</v>
@@ -6911,7 +7148,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>443</v>
+        <v>547</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>78</v>
@@ -7015,7 +7252,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>444</v>
+        <v>548</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>78</v>
@@ -7119,7 +7356,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>445</v>
+        <v>549</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>78</v>
@@ -7223,7 +7460,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>446</v>
+        <v>550</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>78</v>
